--- a/packages/examples/showcase/native-excel-forecast-table/artifact/native-excel-forecast-table.xlsx
+++ b/packages/examples/showcase/native-excel-forecast-table/artifact/native-excel-forecast-table.xlsx
@@ -244,22 +244,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ForecastTable" displayName="ForecastTable" ref="A1:G12" totalsRowCount="1" headerRowCount="1">
-  <autoFilter ref="A1:G11"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="Rep" totalsRowLabel="TOTAL"/>
-    <tableColumn id="2" name="Territory"/>
-    <tableColumn id="3" name="Stage"/>
-    <tableColumn id="4" name="Units" totalsRowFunction="sum"/>
-    <tableColumn id="5" name="Revenue" totalsRowFunction="sum"/>
-    <tableColumn id="6" name="Avg Price" totalsRowLabel="-">
-      <calculatedColumnFormula>ROUND((ForecastTable[@[Revenue]]/ForecastTable[@[Units]]),2)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" name="Close Month" totalsRowFunction="max"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?><table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ForecastTable" displayName="ForecastTable" ref="A1:G12" totalsRowCount="1" headerRowCount="1"><autoFilter ref="A1:G11"/><tableColumns count="7"><tableColumn id="1" name="Rep" totalsRowLabel="TOTAL"/><tableColumn id="2" name="Territory"/><tableColumn id="3" name="Stage"/><tableColumn id="4" name="Units" totalsRowFunction="sum"/><tableColumn id="5" name="Revenue" totalsRowFunction="sum"/><tableColumn id="6" name="Avg Price" totalsRowLabel="-"><calculatedColumnFormula>ROUND(IF((ForecastTable[@[Units]]<>0),(ForecastTable[@[Revenue]]/ForecastTable[@[Units]]),0),2)</calculatedColumnFormula></tableColumn><tableColumn id="7" name="Close Month" totalsRowFunction="max"/></tableColumns><tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/></table>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -316,7 +301,7 @@
         <v>307415</v>
       </c>
       <c r="F2" s="5">
-        <f>ROUND(([@[Revenue]]/[@[Units]]),2)</f>
+        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
       </c>
       <c r="G2" s="2" t="s">
         <v>10</v>
@@ -339,7 +324,7 @@
         <v>185220</v>
       </c>
       <c r="F3" s="5">
-        <f>ROUND(([@[Revenue]]/[@[Units]]),2)</f>
+        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
       </c>
       <c r="G3" s="2" t="s">
         <v>14</v>
@@ -362,7 +347,7 @@
         <v>396734</v>
       </c>
       <c r="F4" s="5">
-        <f>ROUND(([@[Revenue]]/[@[Units]]),2)</f>
+        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
       </c>
       <c r="G4" s="2" t="s">
         <v>18</v>
@@ -385,7 +370,7 @@
         <v>356112</v>
       </c>
       <c r="F5" s="5">
-        <f>ROUND(([@[Revenue]]/[@[Units]]),2)</f>
+        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -408,7 +393,7 @@
         <v>325532</v>
       </c>
       <c r="F6" s="5">
-        <f>ROUND(([@[Revenue]]/[@[Units]]),2)</f>
+        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
       </c>
       <c r="G6" s="2" t="s">
         <v>14</v>
@@ -431,7 +416,7 @@
         <v>181200</v>
       </c>
       <c r="F7" s="5">
-        <f>ROUND(([@[Revenue]]/[@[Units]]),2)</f>
+        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -454,7 +439,7 @@
         <v>218137</v>
       </c>
       <c r="F8" s="5">
-        <f>ROUND(([@[Revenue]]/[@[Units]]),2)</f>
+        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
       </c>
       <c r="G8" s="2" t="s">
         <v>27</v>
@@ -477,7 +462,7 @@
         <v>181799</v>
       </c>
       <c r="F9" s="5">
-        <f>ROUND(([@[Revenue]]/[@[Units]]),2)</f>
+        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
       </c>
       <c r="G9" s="2" t="s">
         <v>14</v>
@@ -500,7 +485,7 @@
         <v>93641</v>
       </c>
       <c r="F10" s="5">
-        <f>ROUND(([@[Revenue]]/[@[Units]]),2)</f>
+        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
       </c>
       <c r="G10" s="2" t="s">
         <v>10</v>
@@ -523,7 +508,7 @@
         <v>160048</v>
       </c>
       <c r="F11" s="5">
-        <f>ROUND(([@[Revenue]]/[@[Units]]),2)</f>
+        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
       </c>
       <c r="G11" s="2" t="s">
         <v>14</v>

--- a/packages/examples/showcase/native-excel-forecast-table/artifact/native-excel-forecast-table.xlsx
+++ b/packages/examples/showcase/native-excel-forecast-table/artifact/native-excel-forecast-table.xlsx
@@ -4,6 +4,7 @@
   <sheets>
     <sheet name="Forecast Table" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -244,7 +245,22 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?><table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ForecastTable" displayName="ForecastTable" ref="A1:G12" totalsRowCount="1" headerRowCount="1"><autoFilter ref="A1:G11"/><tableColumns count="7"><tableColumn id="1" name="Rep" totalsRowLabel="TOTAL"/><tableColumn id="2" name="Territory"/><tableColumn id="3" name="Stage"/><tableColumn id="4" name="Units" totalsRowFunction="sum"/><tableColumn id="5" name="Revenue" totalsRowFunction="sum"/><tableColumn id="6" name="Avg Price" totalsRowLabel="-"><calculatedColumnFormula>ROUND(IF((ForecastTable[@[Units]]<>0),(ForecastTable[@[Revenue]]/ForecastTable[@[Units]]),0),2)</calculatedColumnFormula></tableColumn><tableColumn id="7" name="Close Month" totalsRowFunction="max"/></tableColumns><tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/></table>
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ForecastTable" displayName="ForecastTable" ref="A1:G12" totalsRowCount="1" headerRowCount="1">
+  <autoFilter ref="A1:G11"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Rep" totalsRowLabel="TOTAL"/>
+    <tableColumn id="2" name="Territory"/>
+    <tableColumn id="3" name="Stage"/>
+    <tableColumn id="4" name="Units" totalsRowFunction="sum"/>
+    <tableColumn id="5" name="Revenue" totalsRowFunction="sum"/>
+    <tableColumn id="6" name="Avg Price" totalsRowLabel="-">
+      <calculatedColumnFormula>ROUND(IF((ForecastTable[[#This Row],[Units]]&lt;&gt;0),(ForecastTable[[#This Row],[Revenue]]/ForecastTable[[#This Row],[Units]]),0),2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" name="Close Month" totalsRowFunction="max"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -301,7 +317,8 @@
         <v>307415</v>
       </c>
       <c r="F2" s="5">
-        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
+        <f>ROUND(IF((ForecastTable[[#This Row],[Units]]&lt;&gt;0),(ForecastTable[[#This Row],[Revenue]]/ForecastTable[[#This Row],[Units]]),0),2)</f>
+        <v>806.86</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>10</v>
@@ -324,7 +341,8 @@
         <v>185220</v>
       </c>
       <c r="F3" s="5">
-        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
+        <f>ROUND(IF((ForecastTable[[#This Row],[Units]]&lt;&gt;0),(ForecastTable[[#This Row],[Revenue]]/ForecastTable[[#This Row],[Units]]),0),2)</f>
+        <v>518.82</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>14</v>
@@ -347,7 +365,8 @@
         <v>396734</v>
       </c>
       <c r="F4" s="5">
-        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
+        <f>ROUND(IF((ForecastTable[[#This Row],[Units]]&lt;&gt;0),(ForecastTable[[#This Row],[Revenue]]/ForecastTable[[#This Row],[Units]]),0),2)</f>
+        <v>740.18</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>18</v>
@@ -370,7 +389,8 @@
         <v>356112</v>
       </c>
       <c r="F5" s="5">
-        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
+        <f>ROUND(IF((ForecastTable[[#This Row],[Units]]&lt;&gt;0),(ForecastTable[[#This Row],[Revenue]]/ForecastTable[[#This Row],[Units]]),0),2)</f>
+        <v>2132.41</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -393,7 +413,8 @@
         <v>325532</v>
       </c>
       <c r="F6" s="5">
-        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
+        <f>ROUND(IF((ForecastTable[[#This Row],[Units]]&lt;&gt;0),(ForecastTable[[#This Row],[Revenue]]/ForecastTable[[#This Row],[Units]]),0),2)</f>
+        <v>682.46</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>14</v>
@@ -416,7 +437,8 @@
         <v>181200</v>
       </c>
       <c r="F7" s="5">
-        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
+        <f>ROUND(IF((ForecastTable[[#This Row],[Units]]&lt;&gt;0),(ForecastTable[[#This Row],[Revenue]]/ForecastTable[[#This Row],[Units]]),0),2)</f>
+        <v>1176.62</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -439,7 +461,8 @@
         <v>218137</v>
       </c>
       <c r="F8" s="5">
-        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
+        <f>ROUND(IF((ForecastTable[[#This Row],[Units]]&lt;&gt;0),(ForecastTable[[#This Row],[Revenue]]/ForecastTable[[#This Row],[Units]]),0),2)</f>
+        <v>565.12</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>27</v>
@@ -462,7 +485,8 @@
         <v>181799</v>
       </c>
       <c r="F9" s="5">
-        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
+        <f>ROUND(IF((ForecastTable[[#This Row],[Units]]&lt;&gt;0),(ForecastTable[[#This Row],[Revenue]]/ForecastTable[[#This Row],[Units]]),0),2)</f>
+        <v>381.13</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>14</v>
@@ -485,7 +509,8 @@
         <v>93641</v>
       </c>
       <c r="F10" s="5">
-        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
+        <f>ROUND(IF((ForecastTable[[#This Row],[Units]]&lt;&gt;0),(ForecastTable[[#This Row],[Revenue]]/ForecastTable[[#This Row],[Units]]),0),2)</f>
+        <v>452.37</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>10</v>
@@ -508,7 +533,8 @@
         <v>160048</v>
       </c>
       <c r="F11" s="5">
-        <f>ROUND(IF(([@[Units]]&lt;&gt;0),([@[Revenue]]/[@[Units]]),0),2)</f>
+        <f>ROUND(IF((ForecastTable[[#This Row],[Units]]&lt;&gt;0),(ForecastTable[[#This Row],[Revenue]]/ForecastTable[[#This Row],[Units]]),0),2)</f>
+        <v>1379.72</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>14</v>
@@ -520,9 +546,11 @@
       </c>
       <c r="D12" s="7">
         <f>SUBTOTAL(109,[Units])</f>
+        <v>3258</v>
       </c>
       <c r="E12" s="8">
         <f>SUBTOTAL(109,[Revenue])</f>
+        <v>2405838</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>35</v>
